--- a/data/trans_orig/P77_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P77_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cual es la persona sustentadora principal del hogar en 2023</t>
+          <t>Población según cual es la persona sustentadora principal del hogar en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>52785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>426317</t>
+          <t>426001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>469694</t>
+          <t>469321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>456605</t>
+          <t>458557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>514173</t>
+          <t>510330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>462303</t>
+          <t>461489</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>490365</t>
+          <t>490409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>285454</t>
+          <t>285245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>328954</t>
+          <t>328262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>754372</t>
+          <t>758991</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>812055</t>
+          <t>810449</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297226</t>
+          <t>292635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509408</t>
+          <t>507106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>924960</t>
+          <t>924309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1382204</t>
+          <t>1362805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1285107</t>
+          <t>1250734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1954188</t>
+          <t>1927038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,47 +1349,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>19673</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>33752</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>19673</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>10872</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>33194</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1774018</t>
+          <t>1773775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1990582</t>
+          <t>1992010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>848391</t>
+          <t>866262</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1301514</t>
+          <t>1300663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2558001</t>
+          <t>2577716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3229169</t>
+          <t>3249999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54404</t>
+          <t>55469</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96106</t>
+          <t>96147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>141935</t>
+          <t>141736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185305</t>
+          <t>183069</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>205812</t>
+          <t>207175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>268252</t>
+          <t>265363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>550517</t>
+          <t>550476</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>592219</t>
+          <t>591154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>472919</t>
+          <t>474237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>516663</t>
+          <t>516859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1035998</t>
+          <t>1040110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1098343</t>
+          <t>1097736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>422727</t>
+          <t>421795</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>613930</t>
+          <t>618631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1530112</t>
+          <t>1535667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2048508</t>
+          <t>2051972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1988628</t>
+          <t>1987446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2717510</t>
+          <t>2672331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23589</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>38834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2828009</t>
+          <t>2823012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3016529</t>
+          <t>3021169</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1594497</t>
+          <t>1588571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2108516</t>
+          <t>2103520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4368223</t>
+          <t>4412395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5091548</t>
+          <t>5100339</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
